--- a/financial_advisor_forms/031_income_survey--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/031_income_survey--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1079,8 +1079,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'group_a'}</t>
+          <t>group_a</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Group A'}</t>
+          <t>Group A</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'group_b'}</t>
+          <t>group_b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Group B'}</t>
+          <t>Group B</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'group_c'}</t>
+          <t>group_c</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Group C'}</t>
+          <t>Group C</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'group_d'}</t>
+          <t>group_d</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Group D'}</t>
+          <t>Group D</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
